--- a/deliverables/coolinens-launch/bulk/COOLINENS_Exact_All_Keywords_Summary_20261004.xlsx
+++ b/deliverables/coolinens-launch/bulk/COOLINENS_Exact_All_Keywords_Summary_20261004.xlsx
@@ -480,7 +480,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Review copy only, do not upload. Adds to the live Phase 1 (10 tests + branded); no keyword duplicates a live one. Bids = max profitable CPC at the go-live price, down-only, no placement modifier.</t>
+          <t>Review copy only, do not upload. Adds to the live Phase 1 (10 tests + branded); no keyword duplicates a live one. Bids = max profitable CPC at the go-live price, fixed bids, no placement modifier.</t>
         </is>
       </c>
     </row>
